--- a/output/full_scan/batch_seq7_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6584</v>
+        <v>6727</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>874.4260268470838</v>
+        <v>1163.22187690814</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>682</v>
+        <v>537</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>69.59532322199507</v>
+        <v>69.0697732856256</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27.40744232591992</v>
+        <v>24.16003360824555</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.542602684708379</v>
+        <v>1.922187690814064</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>13.21778321459319</v>
+        <v>13.10301444161366</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6727</v>
+        <v>6668</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>848.2218769081406</v>
+        <v>1139</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>537</v>
+        <v>44.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.06977328661662</v>
+        <v>73.71571282610589</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.16003361063817</v>
+        <v>24.4632064960873</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.922187690814064</v>
+        <v>8.744885617741145</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>13.10301444167091</v>
+        <v>0.958759836681626</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6642</v>
+        <v>6805</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>809.7749144968044</v>
+        <v>1074.822790897141</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82.7</v>
+        <v>2345</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>56.74757574877992</v>
+        <v>72.63471258786319</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.00358855934157</v>
+        <v>28.19384762677937</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.620174226603708</v>
+        <v>1.582279089714106</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0447747084647296</v>
+        <v>48.87365360371408</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6761</v>
+        <v>6584</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>762.9641579847636</v>
+        <v>1074.426026847084</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>188.5</v>
+        <v>682</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.52630482285026</v>
+        <v>69.59532329684338</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.49811845392306</v>
+        <v>27.40744238810987</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8481962733356799</v>
+        <v>4.542602684708379</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.849910257602064</v>
+        <v>13.21778321115911</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6805</v>
+        <v>6669</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>749.8227908971411</v>
+        <v>1024.400853101634</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2345</v>
+        <v>7200</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>72.63471258338686</v>
+        <v>73.43878608955646</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>28.19384754529619</v>
+        <v>29.1007621962235</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.582279089714106</v>
+        <v>1.196316605178939</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>48.87365360447716</v>
+        <v>49.0655652558986</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6588</v>
+        <v>6642</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>729.9991021802022</v>
+        <v>949.7749144968044</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>112</v>
+        <v>82.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>63.45115682011014</v>
+        <v>56.74757574645579</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.29801754366251</v>
+        <v>16.00358857583793</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.799910218020221</v>
+        <v>0.620174226603708</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.993109049094778</v>
+        <v>0.0447747085028862</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6577</v>
+        <v>6672</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>710.7664238196745</v>
+        <v>931.258950529064</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>80.8</v>
+        <v>289.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>51.91725280520168</v>
+        <v>62.40120062145881</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.05886134159307</v>
+        <v>20.17111682578102</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.319498757696878</v>
+        <v>0.8710016476818362</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,11 +888,11 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.0353601950334892</v>
+        <v>2.266229756376374</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>697.507719843477</v>
+        <v>897.5077198434791</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1140</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.84535270945484</v>
+        <v>59.84535265578624</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10.14009234966542</v>
+        <v>10.14009234888287</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>3.593817561816644</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>17.64485128000672</v>
+        <v>17.64485128677988</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6538</v>
+        <v>6782</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>689.6175719764822</v>
+        <v>865.8634466721837</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>200</v>
+        <v>241.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.06728984176407</v>
+        <v>72.56966489676515</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>37.29412841235212</v>
+        <v>28.17363141837331</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9844341915651936</v>
+        <v>1.89515349689344</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.426650339593444</v>
+        <v>4.46891913218461</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6782</v>
+        <v>6588</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>675.8634466721837</v>
+        <v>844.9991021802022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>241.5</v>
+        <v>112</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>72.56966491020964</v>
+        <v>63.45115681481689</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>28.17363140370436</v>
+        <v>25.2980175391931</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.89515349689344</v>
+        <v>0.799910218020221</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4.468919132756989</v>
+        <v>1.993109049228332</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>663.3057959634539</v>
+        <v>803.3057959634539</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>176.5</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.4055894572972</v>
+        <v>55.40558948946048</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.20190791537143</v>
+        <v>15.20190792435246</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.516720591700334</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.3866006509643611</v>
+        <v>0.3866006505064681</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6716</v>
+        <v>6573</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>653.7461193576609</v>
+        <v>795.3293547390473</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>128</v>
+        <v>18.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>65.39558715125314</v>
+        <v>55.35606632480091</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>34.83015795172624</v>
+        <v>17.51690095362048</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6132065788672342</v>
+        <v>2.15233436471686</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.3839147578992534</v>
+        <v>0.3062789975528383</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>650.992320477229</v>
+        <v>765.992320477229</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>89.2</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.19867048208634</v>
+        <v>61.19867030853811</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.91000237457104</v>
+        <v>32.9100026178242</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.6414303927844275</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.6638243167991407</v>
+        <v>0.6638243171807359</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6651</v>
+        <v>6761</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>618.5833641457172</v>
+        <v>762.9641579847636</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>150.5</v>
+        <v>188.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.21474563551143</v>
+        <v>61.52630482697205</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.04556985087225</v>
+        <v>21.49811851940222</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.408612689603955</v>
+        <v>0.8481962733356799</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.948975787285642</v>
+        <v>1.849910257334954</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6753</v>
+        <v>6651</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>594.0652109991279</v>
+        <v>758.583364145717</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>138.5</v>
+        <v>150.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>47.60130192831053</v>
+        <v>64.21474562447983</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25.70789710296066</v>
+        <v>26.04556990371592</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.674982002348506</v>
+        <v>1.408612689603955</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.349200914975865</v>
+        <v>1.948975787056668</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6491</v>
+        <v>6743</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>588.1394526510223</v>
+        <v>739.9927057498001</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>377</v>
+        <v>27.85</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.0115932182643</v>
+        <v>54.51581453081894</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.28732335793201</v>
+        <v>22.83648663360617</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5776127103074311</v>
+        <v>1.570195178023184</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.3012050450158625</v>
+        <v>0.3309682994949462</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6788</v>
+        <v>6577</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>565.1050084055137</v>
+        <v>710.7664238196745</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>368.5</v>
+        <v>80.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.26504081048315</v>
+        <v>51.91725277193699</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.74179212119917</v>
+        <v>24.05886137171666</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.144354839849481</v>
+        <v>0.319498757696878</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.498524508653589</v>
+        <v>-0.0353601949953202</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6664</v>
+        <v>6788</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>530.3499761138836</v>
+        <v>705.1050084055133</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>359.5</v>
+        <v>368.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.73157816346845</v>
+        <v>55.26504091168285</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15.50598244770173</v>
+        <v>21.74179216163353</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6464095842359011</v>
+        <v>1.144354839849481</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.993140837940043</v>
+        <v>3.498524507222642</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6517</v>
+        <v>6829</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>528.9401620667236</v>
+        <v>704.2112549823761</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>238</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.50279793051006</v>
+        <v>60.89091199385354</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.27358730218311</v>
+        <v>17.46677272334954</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.485885197386855</v>
+        <v>1.129807832306887</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,51 +1524,51 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.102611121682565</v>
+        <v>3.159386522598669</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6806</v>
+        <v>6517</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>698.9401620667237</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>3.51</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>31.69502661425305</v>
+        <v>59.50279806223553</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32.59319880613012</v>
+        <v>17.27358757298257</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.485885197386855</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4112821212078614</v>
+        <v>1.102611120900306</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6597</v>
+        <v>6491</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>511.6491017508395</v>
+        <v>698.1394526510223</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>377</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>52.33673321732065</v>
+        <v>59.01159323429387</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>8.261296327836822</v>
+        <v>24.28732348979456</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3712961420010245</v>
+        <v>0.5776127103074311</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1551092183204865</v>
+        <v>-0.3012050458744255</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6829</v>
+        <v>6526</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>504.2112549823761</v>
+        <v>694.9991462170708</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>238</v>
+        <v>620</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.89091200496722</v>
+        <v>56.02819333824144</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>17.4667727771627</v>
+        <v>13.8214231469664</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.129807832306887</v>
+        <v>0.6576053200245886</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.159386522980263</v>
+        <v>3.428398430426454</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6505</v>
+        <v>6538</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>501.7792549297543</v>
+        <v>689.6175719764822</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>200</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.03609051990609</v>
+        <v>63.06728984502333</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.6698175674976</v>
+        <v>37.29412845817093</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4667233320255103</v>
+        <v>0.9844341915651936</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2329322160663287</v>
+        <v>2.426650339326319</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6486</v>
+        <v>6831</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>500.2007594055802</v>
+        <v>682.1593173995115</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>620</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>61.0998850816432</v>
+        <v>49.50265843340998</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22.88248586868419</v>
+        <v>15.94640147577665</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6496121050915438</v>
+        <v>1.279502135138927</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6092324742120119</v>
+        <v>0.7397976770979184</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6488</v>
+        <v>6613</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>500.0355570798037</v>
+        <v>657.2819026332706</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>972</v>
+        <v>275.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.58148436062476</v>
+        <v>50.11115413691734</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.59383574375703</v>
+        <v>10.84005700583362</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.015038703077769</v>
+        <v>1.733661985709542</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>6.213706699962771</v>
+        <v>2.909619698642615</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6613</v>
+        <v>6716</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>487.2819026332706</v>
+        <v>653.7461193576607</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>275.5</v>
+        <v>128</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.11115412778243</v>
+        <v>65.39558714620318</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.84005695975428</v>
+        <v>34.83015800658413</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.733661985709542</v>
+        <v>0.6132065788672342</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.90961969883335</v>
+        <v>0.3839147577847761</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6494</v>
+        <v>6830</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>477.7237509232833</v>
+        <v>642.2510139674524</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>54.9</v>
+        <v>525</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.68860515254076</v>
+        <v>65.16438755805815</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12.53704408261979</v>
+        <v>24.64192422338555</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4881462784004069</v>
+        <v>0.6235192162794566</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.329434554851274</v>
+        <v>15.17610356326843</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6743</v>
+        <v>6486</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>459.9927057498001</v>
+        <v>640.2007594055802</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>27.85</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.51581452209805</v>
+        <v>61.09988519090607</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.83648659990237</v>
+        <v>22.88248592879861</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.570195178023184</v>
+        <v>0.6496121050915438</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3309682995712635</v>
+        <v>0.6092324740212161</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6789</v>
+        <v>6533</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>454.889449984017</v>
+        <v>628.799039268437</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>461</v>
+        <v>265.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.8605875737813</v>
+        <v>65.24107772203082</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.11721378388251</v>
+        <v>16.22905340435587</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.193877795191994</v>
+        <v>0.4715686631482062</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>5.602716355716337</v>
+        <v>1.311497577759413</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6530</v>
+        <v>6789</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>447.6500170520897</v>
+        <v>624.889449984017</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>461</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.48973798983035</v>
+        <v>53.86058760535675</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15.14166031445574</v>
+        <v>21.11721387308983</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.111801872303157</v>
+        <v>1.193877795191994</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,11 +2107,11 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.912328975062746</v>
+        <v>5.602716354857755</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>447.4271583869129</v>
+        <v>617.4271583869129</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>59.2</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.04044281025041</v>
+        <v>61.04044279620752</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.81413166981678</v>
+        <v>26.81413163594944</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.148373886940966</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.6975963030445002</v>
+        <v>0.6975963029109415</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6598</v>
+        <v>6488</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>445.1668246271737</v>
+        <v>615.3392905561025</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>28.75</v>
+        <v>972</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.0810771793248</v>
+        <v>48.58148436491808</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.13280045569584</v>
+        <v>11.59383585949848</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5306839305471628</v>
+        <v>1.035920898167337</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1163768050232211</v>
+        <v>6.213706698531823</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6830</v>
+        <v>6670</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>442.251013967452</v>
+        <v>601.0235411748481</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>525</v>
+        <v>272.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>65.16438756122244</v>
+        <v>57.09060788682248</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.64192417312219</v>
+        <v>17.56798474905304</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6235192162794566</v>
+        <v>0.9245349659120452</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>15.17610356345919</v>
+        <v>0.9841289138626084</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6640</v>
+        <v>6693</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>439.4729542386274</v>
+        <v>595.0340044878492</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1060</v>
+        <v>178.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.67538409538767</v>
+        <v>51.4286478281998</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.69834540865102</v>
+        <v>14.68773845857429</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8345518023660453</v>
+        <v>2.233006903882091</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>10.38766883076058</v>
+        <v>0.9486066506198956</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6831</v>
+        <v>6530</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>437.1593173995113</v>
+        <v>587.6500170520898</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>620</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.50265841186888</v>
+        <v>56.48973802157072</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.94640139068774</v>
+        <v>15.14166040952995</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.279502135138927</v>
+        <v>1.111801872303157</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7397976778610342</v>
+        <v>0.9123289749101196</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6770</v>
+        <v>6753</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>435.7203873420583</v>
+        <v>579.0652109991279</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>70</v>
+        <v>138.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.57990552794572</v>
+        <v>47.60130190859052</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.11717861918472</v>
+        <v>25.7078971379036</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5440650885342839</v>
+        <v>1.674982002348506</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.151414723906507</v>
+        <v>-0.3492009147850683</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6605</v>
+        <v>6834</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>435.7078607722104</v>
+        <v>572.9615313010128</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>139</v>
+        <v>94.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.82892541499323</v>
+        <v>49.12359706419669</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.52980083841325</v>
+        <v>11.86006304811672</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7821202818711557</v>
+        <v>1.157778579397804</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0912457295239508</v>
+        <v>-0.2927564067694699</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6670</v>
+        <v>6515</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>426.0235411748482</v>
+        <v>567.6300623872738</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>272.5</v>
+        <v>6250</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.09060761483124</v>
+        <v>43.7668472762364</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17.5679845791525</v>
+        <v>16.53301173182521</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9245349659120452</v>
+        <v>0.7885279568100498</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.9841289189186536</v>
+        <v>7.393261131448213</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6693</v>
+        <v>6525</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>425.0340044878493</v>
+        <v>556.7683265087962</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>178.5</v>
+        <v>144.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.42864781940541</v>
+        <v>51.27095477635569</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.68773845735759</v>
+        <v>11.20535786539205</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.233006903882091</v>
+        <v>1.058845741832299</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>1</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.9486066506580526</v>
+        <v>0.7075425632728782</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>416.5412932548287</v>
+        <v>556.5412932548287</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>63.8</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>49.8080532626515</v>
+        <v>49.8080532796088</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.14529107830037</v>
+        <v>20.14529117597636</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.15216566495413</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.7489471092819762</v>
+        <v>0.7489471091293423</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6715</v>
+        <v>6658</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>408.3699446860068</v>
+        <v>543.7502689084668</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>353.5</v>
+        <v>166.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>43.51772867004992</v>
+        <v>52.95210209148745</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.77516070422614</v>
+        <v>11.99557448236283</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6190584335317496</v>
+        <v>1.296948643169257</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-4.634114470778742</v>
+        <v>1.849190046410996</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6796</v>
+        <v>6664</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>403.1010769607283</v>
+        <v>530.3499761138828</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>61.6</v>
+        <v>359.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.86520356155052</v>
+        <v>52.7315781861441</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.61888115874072</v>
+        <v>15.50598265414119</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7245113885577742</v>
+        <v>0.6464095842359011</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,48 +2743,48 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1983613442472102</v>
+        <v>2.993140836413749</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6771</v>
+        <v>6806</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>394.7790862729152</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>41</v>
+        <v>3.51</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.78854689711553</v>
+        <v>31.69502639099356</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>40.14207082820065</v>
+        <v>32.59319844291417</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5545833794809318</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0898075708067155</v>
+        <v>0.4112821135359059</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>393.5812010569701</v>
+        <v>514.3191902693231</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>32.6</v>
+        <v>49.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.77813491353292</v>
+        <v>52.66286654313096</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.05139117099468</v>
+        <v>27.114192009729</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.205344392580274</v>
+        <v>0.5757158935641449</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1303608129574077</v>
+        <v>-0.1048727779104106</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6666</v>
+        <v>6597</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>379.9821391209524</v>
+        <v>511.6491017508397</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>44.1</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.561903895306</v>
+        <v>52.33673321516893</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.67692479494261</v>
+        <v>8.261296323278277</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2722520105835063</v>
+        <v>0.3712961420010245</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1458661513137023</v>
+        <v>0.1551092183204865</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6834</v>
+        <v>6505</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>367.9615313010128</v>
+        <v>501.7792549297543</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>94.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.12359706628378</v>
+        <v>51.03609050821652</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.86006297794728</v>
+        <v>26.66981767207194</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.157778579397804</v>
+        <v>0.4667233320255103</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.2927564067313071</v>
+        <v>-0.232932216114037</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6645</v>
+        <v>6683</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>363.0929249354143</v>
+        <v>501.4763975316008</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12.4</v>
+        <v>1200</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>34.09815065476057</v>
+        <v>48.43108316729182</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.89144037027991</v>
+        <v>17.92258239179225</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.026577576391844</v>
+        <v>1.905808120669373</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.009035417837622999</v>
+        <v>11.34282990409182</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6691</v>
+        <v>6494</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>356.2914708570562</v>
+        <v>477.7237509232833</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>618</v>
+        <v>54.9</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>36.99403127785696</v>
+        <v>52.68860517490503</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.91119477829358</v>
+        <v>12.53704408261979</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7583069154427319</v>
+        <v>0.4881462784004069</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-8.53846768852069</v>
+        <v>0.329434554774952</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6792</v>
+        <v>6691</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>354.1631467227314</v>
+        <v>471.2914708570564</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>59.5</v>
+        <v>618</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.27102531251768</v>
+        <v>36.9940313319426</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.67904865097726</v>
+        <v>21.91119485530072</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4356724249025804</v>
+        <v>0.7583069154427319</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.3377382294463009</v>
+        <v>-8.538467690428604</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6708</v>
+        <v>6792</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>352.0391757433389</v>
+        <v>464.1631467227314</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>37.1</v>
+        <v>59.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.98616809412766</v>
+        <v>55.27102529151247</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.385002977801477</v>
+        <v>14.67904860500375</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.603917574333893</v>
+        <v>0.4356724249025804</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,11 +3167,11 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.2731355961865991</v>
+        <v>0.3377382294844514</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>341.929338471936</v>
+        <v>456.929338471936</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>131</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.51310593799072</v>
+        <v>43.51310608146494</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>42.06428507488543</v>
+        <v>42.06428511816397</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.6069313908684988</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.262364107833789</v>
+        <v>1.262364105735066</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6821</v>
+        <v>6698</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>334.218319854483</v>
+        <v>456.6658783542237</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>41.95</v>
+        <v>32.35</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.43022653213342</v>
+        <v>46.390495056824</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.33696093031526</v>
+        <v>22.88325001164543</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.581618562645051</v>
+        <v>0.609985651192758</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.604321413510347</v>
+        <v>0.3025016283654831</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6606</v>
+        <v>6706</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>333.8805197348667</v>
+        <v>456.424637183426</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>26.1</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.91137567126369</v>
+        <v>54.33708474011213</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>13.71202156797134</v>
+        <v>14.68901778697491</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4509898603219103</v>
+        <v>0.6600401894667781</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0744025053629916</v>
+        <v>1.954885484641729</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6683</v>
+        <v>6598</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>331.4763975316008</v>
+        <v>445.1668246271737</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1200</v>
+        <v>28.75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.43108316612081</v>
+        <v>54.0810771460155</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>17.92258235099</v>
+        <v>23.13280039952096</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.905808120669373</v>
+        <v>0.5306839305471628</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>11.34282990552263</v>
+        <v>-0.1163768049850649</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6561</v>
+        <v>6640</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>331.0523211736604</v>
+        <v>439.4729542386277</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>322.5</v>
+        <v>1060</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.32715125296674</v>
+        <v>55.6753840736852</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10.11422085826729</v>
+        <v>17.69834542150458</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7330310779974486</v>
+        <v>0.8345518023660453</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2863376472386534</v>
+        <v>10.38766883381332</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6589</v>
+        <v>6680</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>329.3191902693231</v>
+        <v>437.1892327012965</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>49.85</v>
+        <v>50</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.66286647367839</v>
+        <v>51.41423642244175</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>27.11419196479077</v>
+        <v>7.762920021925661</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5757158935641449</v>
+        <v>0.2142981253740564</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1048727777386877</v>
+        <v>1.808982354830126</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6498</v>
+        <v>6605</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>327.766139512952</v>
+        <v>435.7078607722104</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>139</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.08152681322862</v>
+        <v>52.82892520531984</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.90982202540357</v>
+        <v>14.52980082966979</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.645832291211158</v>
+        <v>0.7821202818711557</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.8232466624821209</v>
+        <v>0.0912457301917375</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6692</v>
+        <v>6581</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>327.2780307932242</v>
+        <v>426.7618374925132</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.3</v>
+        <v>109.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.38362417989234</v>
+        <v>60.15122835190314</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.671514561326273</v>
+        <v>24.39176103762082</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.42737515225335</v>
+        <v>1.232190007270686</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1072787369748725</v>
+        <v>0.1557858106787006</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6690</v>
+        <v>6770</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>318.3605437623369</v>
+        <v>425.7203873420583</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.61979706842511</v>
+        <v>52.57990551265148</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10.7823441063283</v>
+        <v>13.11717870258828</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.265684622681145</v>
+        <v>0.5440650885342839</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2647601751206432</v>
+        <v>0.1514147238397262</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6706</v>
+        <v>6794</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>316.4246371834261</v>
+        <v>408.5301806272269</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>124</v>
+        <v>78.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.33708474153612</v>
+        <v>59.30807747858573</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.68901769231417</v>
+        <v>23.85923390617952</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6600401894667781</v>
+        <v>0.6859947272192183</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.954885484813435</v>
+        <v>1.056446569756034</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6624</v>
+        <v>6715</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>311.869459967988</v>
+        <v>408.3699446860068</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>41.65</v>
+        <v>353.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.07544898808017</v>
+        <v>43.51772866211385</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5.695763794470844</v>
+        <v>13.77516084261178</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.047977124507035</v>
+        <v>0.6190584335317496</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1582673190536363</v>
+        <v>-4.634114470969585</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6689</v>
+        <v>6796</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>308.864790574012</v>
+        <v>403.1010769607283</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>62.3</v>
+        <v>61.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.94793909709045</v>
+        <v>54.86520353140563</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.14153306179221</v>
+        <v>29.61888110313754</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.168157680063443</v>
+        <v>0.7245113885577742</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1697362441113889</v>
+        <v>0.1983613440373275</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6655</v>
+        <v>6771</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>305.6637155803742</v>
+        <v>394.7790862729152</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.3018384924452</v>
+        <v>51.78854709562391</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.42388724749577</v>
+        <v>40.14207089351221</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2171599817585615</v>
+        <v>0.5545833794809318</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0522262470322822</v>
+        <v>0.08980757063499541</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6742</v>
+        <v>6582</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>304.4316408637956</v>
+        <v>393.58120105697</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>44.55</v>
+        <v>32.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.19192683855668</v>
+        <v>56.77813485111609</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.27285451965061</v>
+        <v>22.051391348878</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.51141172224243</v>
+        <v>1.205344392580274</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6191606144243456</v>
+        <v>0.1303608127761544</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6512</v>
+        <v>6695</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>304.2241961825587</v>
+        <v>389.2700787164352</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>20.6</v>
+        <v>49.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.48428893605124</v>
+        <v>47.47949348827306</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10.31251828616872</v>
+        <v>16.39236305698185</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3584169219792672</v>
+        <v>1.472704412067508</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.265273796851079</v>
+        <v>0.1600024869223368</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6756</v>
+        <v>6781</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>300.4298965723606</v>
+        <v>383.7672234580476</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100</v>
+        <v>1130</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.47793201951458</v>
+        <v>56.61747880779102</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>10.89798027319086</v>
+        <v>13.39344347774733</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5983765741696949</v>
+        <v>1.423718903058465</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2390598918041293</v>
+        <v>4.19975858880482</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6763</v>
+        <v>6679</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>299.2146750420882</v>
+        <v>383.258856076063</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>41.85</v>
+        <v>205</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>43.51688704842103</v>
+        <v>43.82323002604752</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.17297974415653</v>
+        <v>24.08024905111672</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.920086422623036</v>
+        <v>1.096255317502106</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0728905487216947</v>
+        <v>1.695367538476152</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6803</v>
+        <v>6666</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>298.1919854951188</v>
+        <v>379.9821391209524</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>271</v>
+        <v>44.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.12508572247303</v>
+        <v>53.56190384830151</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.78074647991012</v>
+        <v>19.67692482515929</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9709698374763842</v>
+        <v>0.2722520105835063</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.5359135010537142</v>
+        <v>0.1458661513995546</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6722</v>
+        <v>6591</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>297.6696358643652</v>
+        <v>379.6908426599418</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>32.7</v>
+        <v>42.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.42195449420166</v>
+        <v>37.9935326332063</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>34.5219949630516</v>
+        <v>30.5931095663557</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.9142284013350226</v>
+        <v>1.043243369869631</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1444143608481501</v>
+        <v>0.099126051925914</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6671</v>
+        <v>6558</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>297.5052112607708</v>
+        <v>372.6075616234936</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>23</v>
+        <v>25.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.32206662237247</v>
+        <v>46.78969122561927</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.87259132227537</v>
+        <v>27.32977163490825</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.088161105756414</v>
+        <v>0.6456624235459237</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1340205643074212</v>
+        <v>0.1617747016324535</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6811</v>
+        <v>6674</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>276.8264654298148</v>
+        <v>364.7672536308446</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>225.5</v>
+        <v>16</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.0207439769526</v>
+        <v>52.5880092950655</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.30316699501042</v>
+        <v>26.35171375837841</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3019415358134989</v>
+        <v>0.3391371061929172</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.61352374948652</v>
+        <v>0.1600429018571639</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6510</v>
+        <v>6645</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>276.4743432205681</v>
+        <v>363.0929249354143</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>2680</v>
+        <v>12.4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.97024865774408</v>
+        <v>34.09815095979685</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.25513987796363</v>
+        <v>26.89144038823786</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9974480180655456</v>
+        <v>3.026577576391844</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.148539403225953</v>
+        <v>-0.009035417990257101</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6695</v>
+        <v>6548</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>274.2700787164352</v>
+        <v>362.9112560543358</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>49.2</v>
+        <v>73.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>47.47949345316349</v>
+        <v>51.29218791136723</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.39236299928172</v>
+        <v>12.63748790067431</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.472704412067508</v>
+        <v>0.9994370840342768</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1600024870845149</v>
+        <v>0.4696252818734037</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6719</v>
+        <v>6643</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>271.0085070418895</v>
+        <v>360.8395461590009</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>194.5</v>
+        <v>437</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>38.60285684186113</v>
+        <v>52.34552061036856</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23.67348381250712</v>
+        <v>14.15567532458209</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8805800033822218</v>
+        <v>0.6396858457570336</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.9710655109532896</v>
+        <v>2.946044554892074</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6585</v>
+        <v>6531</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>268.5771916364242</v>
+        <v>360.461280349692</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>114.5</v>
+        <v>895</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.46512290832134</v>
+        <v>52.43290989996926</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.85309971714472</v>
+        <v>8.963528077862794</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.335870481677022</v>
+        <v>0.9559002841166534</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0221182006203624</v>
+        <v>7.122874720590955</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6679</v>
+        <v>6708</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>268.258856076063</v>
+        <v>352.0391757433389</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>205</v>
+        <v>37.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.82322999152078</v>
+        <v>50.98616809308466</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.08024902282249</v>
+        <v>8.385002994715375</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.096255317502106</v>
+        <v>1.603917574333893</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.695367539334752</v>
+        <v>0.2731355962152202</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6732</v>
+        <v>6821</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>265.1701280742709</v>
+        <v>334.218319854483</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>154</v>
+        <v>41.95</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.79887754734904</v>
+        <v>44.43022657162763</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.57405862786615</v>
+        <v>18.33696093918741</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.090081128713227</v>
+        <v>1.581618562645051</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.9711032225457376</v>
+        <v>0.6043214134054176</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6807</v>
+        <v>6606</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>252.8568330698958</v>
+        <v>333.8805197348667</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>33.5</v>
+        <v>26.1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.63373828539208</v>
+        <v>49.91137586280552</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.811045469701</v>
+        <v>13.71202185165849</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4595051971090372</v>
+        <v>0.4509898603219103</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.6007434189997769</v>
+        <v>-0.07440250542977241</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6657</v>
+        <v>6561</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>246.840035900737</v>
+        <v>331.0523211736604</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>30.3</v>
+        <v>322.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>43.23909593667988</v>
+        <v>47.32715110807266</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>26.07248449755583</v>
+        <v>10.11422090907316</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4975177838430294</v>
+        <v>0.7330310779974486</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.191571543829814</v>
+        <v>0.2863376476202557</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6768</v>
+        <v>6498</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>241.4518584076877</v>
+        <v>327.766139512952</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>64.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>35.13184177111809</v>
+        <v>47.08152676599166</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>30.93475183436009</v>
+        <v>22.90982214397665</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6325782485463421</v>
+        <v>1.645832291211158</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2991242327447909</v>
+        <v>0.8232466623867323</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6534</v>
+        <v>6692</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>240.8425869563524</v>
+        <v>327.2780307932241</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91.2</v>
+        <v>24.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.98264456758984</v>
+        <v>52.38362417738004</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15.40975335727651</v>
+        <v>9.671514568370418</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5106125488735803</v>
+        <v>1.42737515225335</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.2289029658600168</v>
+        <v>0.1072787369939523</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6794</v>
+        <v>6579</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>238.5301806272268</v>
+        <v>320.2363897543969</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>78.2</v>
+        <v>147</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>59.30807746948518</v>
+        <v>40.29716988843114</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.85923390816561</v>
+        <v>14.47265930968291</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6859947272192183</v>
+        <v>0.4008723001982963</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>1.056446569794189</v>
+        <v>-0.978909539232887</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6625</v>
+        <v>6690</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>237.9542029357949</v>
+        <v>318.3605437623369</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.15690966478158</v>
+        <v>52.61979735865024</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.03662313714298</v>
+        <v>10.78234440122848</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8474926211414581</v>
+        <v>1.265684622681145</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.06807974625413141</v>
+        <v>0.2647601740712673</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6680</v>
+        <v>6671</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>237.1892327012965</v>
+        <v>317.5052112607708</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.41423641992554</v>
+        <v>47.3220665523229</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>7.762919969659932</v>
+        <v>20.87259132227537</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2142981253740564</v>
+        <v>1.088161105756414</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.808982355097242</v>
+        <v>0.1340205643074212</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6757</v>
+        <v>6624</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>233.7473577959741</v>
+        <v>311.869459967988</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>55.1</v>
+        <v>41.65</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.02417929581536</v>
+        <v>53.0754489824614</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.837136339237766</v>
+        <v>5.695763788404508</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.247799484921084</v>
+        <v>0.047977124507035</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0337827935713455</v>
+        <v>0.1582673192253509</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6698</v>
+        <v>6689</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>231.6658783542237</v>
+        <v>308.8647905740121</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>32.35</v>
+        <v>62.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.39049508190727</v>
+        <v>51.94793909709045</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.88324998231029</v>
+        <v>15.14153303573668</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.609985651192758</v>
+        <v>1.168157680063443</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.3025016284418005</v>
+        <v>0.1697362439396728</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6570</v>
+        <v>6655</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>231.3860964970725</v>
+        <v>305.6637155803744</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>51.7</v>
+        <v>116</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>41.76763360884588</v>
+        <v>47.30184639874805</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.11805404178262</v>
+        <v>10.4238876489406</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.633802202302688</v>
+        <v>0.2171599817585615</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.5384795747237363</v>
+        <v>0.0522262230875728</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6548</v>
+        <v>6742</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>222.9112560543357</v>
+        <v>304.4316408637956</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>73.5</v>
+        <v>44.55</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.29218792460954</v>
+        <v>47.19192690148947</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>12.63748782138043</v>
+        <v>16.2728545686686</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9994370840342768</v>
+        <v>1.51141172224243</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.4696252818543228</v>
+        <v>0.619160614138152</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6643</v>
+        <v>6512</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>220.8395461590009</v>
+        <v>304.2241961825587</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>437</v>
+        <v>20.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.34552060119871</v>
+        <v>53.48428893288605</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.15567528878756</v>
+        <v>10.31251828616872</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6396858457570336</v>
+        <v>0.3584169219792672</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.94604455641845</v>
+        <v>-0.2652737968701597</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6546</v>
+        <v>6756</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>218.7434976496474</v>
+        <v>300.4298965723605</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.88236984636117</v>
+        <v>53.47793196543836</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.06068704851056</v>
+        <v>10.89798029612267</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6276581417216501</v>
+        <v>0.5983765741696949</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4254912192543655</v>
+        <v>0.2390598913271435</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6592</v>
+        <v>6763</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>215.6799505614673</v>
+        <v>299.2146750420882</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>60.5</v>
+        <v>41.85</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.89200530765977</v>
+        <v>43.51688734440928</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.32339213467872</v>
+        <v>20.17297967019713</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.42796065595693</v>
+        <v>0.920086422623036</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.064437295633932</v>
+        <v>0.0728905481493094</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6720</v>
+        <v>6803</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>210.1874719835197</v>
+        <v>298.1919854951188</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>133.5</v>
+        <v>271</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.39354731579302</v>
+        <v>50.12508591403759</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>26.21492099757149</v>
+        <v>22.78074643591655</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.929394978777252</v>
+        <v>0.9709698374763842</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1497474400231404</v>
+        <v>0.5359135006720794</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6560</v>
+        <v>6722</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>205.463684471994</v>
+        <v>297.6696358643652</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>31</v>
+        <v>32.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.40058035887137</v>
+        <v>43.42195355774251</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.4204119717172</v>
+        <v>34.52199543600651</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.285201701298458</v>
+        <v>0.9142284013350226</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2901450150651778</v>
+        <v>0.1444143614968518</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6550</v>
+        <v>6811</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>196.8224937055401</v>
+        <v>276.8264654298148</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11.2</v>
+        <v>225.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.25687715586443</v>
+        <v>48.02074388313361</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.0599806898228</v>
+        <v>10.30316708818047</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8042719887368431</v>
+        <v>0.3019415358134989</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1225559272149415</v>
+        <v>-0.6135237488187496</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6781</v>
+        <v>6510</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>193.7672234580476</v>
+        <v>276.4743432205681</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1130</v>
+        <v>2680</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>56.61747878131947</v>
+        <v>46.97024868086654</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.39344343995448</v>
+        <v>12.25513987820543</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.423718903058465</v>
+        <v>0.9974480180655456</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>4.199758591666838</v>
+        <v>1.148539398837372</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6776</v>
+        <v>6735</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>171.2101962687045</v>
+        <v>273.0220751877535</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>53.2</v>
+        <v>63.9</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.00466972023832</v>
+        <v>44.50142761254212</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.70895627517364</v>
+        <v>16.73149670269364</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3638652344808326</v>
+        <v>0.6380625567239551</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0299615602637201</v>
+        <v>0.7455783491352479</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6667</v>
+        <v>6719</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>164.6092193858473</v>
+        <v>271.0085070418895</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>221</v>
+        <v>194.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.20738087920107</v>
+        <v>38.60285678504675</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>29.66349442432439</v>
+        <v>23.67348386974887</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7623102678039883</v>
+        <v>0.8805800033822218</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.8422647869874389</v>
+        <v>0.9710655114302932</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6725</v>
+        <v>6585</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>162.9480484125874</v>
+        <v>268.5771916364242</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>231</v>
+        <v>114.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.01009971717336</v>
+        <v>45.46512288524565</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>30.24332604308669</v>
+        <v>16.85309971761652</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.585394433467616</v>
+        <v>0.335870481677022</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>2.172077716390653</v>
+        <v>0.0221182005249578</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6735</v>
+        <v>6732</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>158.0220751877534</v>
+        <v>265.1701280742709</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>63.9</v>
+        <v>154</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.50142762568452</v>
+        <v>43.79887753234711</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.73149670079175</v>
+        <v>18.5740586291234</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6380625567239551</v>
+        <v>1.090081128713227</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.7455783491352479</v>
+        <v>0.9711032221641648</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6799</v>
+        <v>6807</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>151.0337240580648</v>
+        <v>252.8568330698961</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>80.5</v>
+        <v>33.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.90322746929562</v>
+        <v>34.63373822897739</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.55438174490629</v>
+        <v>22.81104545935737</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6289056521666977</v>
+        <v>0.4595051971090372</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2579152570421437</v>
+        <v>-0.6007434190951713</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6541</v>
+        <v>6556</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>147.8752817203151</v>
+        <v>247.5384303852448</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>36.1</v>
+        <v>61.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>40.6266810555733</v>
+        <v>45.13762697320091</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.96892762093402</v>
+        <v>18.01293539936331</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.423218635419374</v>
+        <v>0.06585572481258289</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0104760222680968</v>
+        <v>0.4381909702486561</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6614</v>
+        <v>6657</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>145.9864144070126</v>
+        <v>246.8400359007369</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>35.9</v>
+        <v>30.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.04079925675395</v>
+        <v>43.23909568948171</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>8.648490293939146</v>
+        <v>26.07248445776182</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.447967948046507</v>
+        <v>0.4975177838430294</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.1412595636980435</v>
+        <v>0.1915715436962579</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6684</v>
+        <v>6552</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>133.3683247401822</v>
+        <v>241.836145216035</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>47.3</v>
+        <v>25.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.15560372565253</v>
+        <v>48.80718696908981</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.72733106068623</v>
+        <v>12.7316741857915</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8523813156250838</v>
+        <v>0.4125009583372075</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1377780762697502</v>
+        <v>0.2505847440540415</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6556</v>
+        <v>6768</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>132.5384303852448</v>
+        <v>241.4518584076877</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>61.3</v>
+        <v>64.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.1376232243368</v>
+        <v>35.13184194942389</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.01293020612069</v>
+        <v>30.93475178487103</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.06585572481258289</v>
+        <v>0.6325782485463421</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.4381909853023389</v>
+        <v>0.2991242326493952</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6835</v>
+        <v>6534</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>122.6713416645746</v>
+        <v>240.8425869563524</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>31.2</v>
+        <v>91.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.50835626335569</v>
+        <v>40.9826564854695</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.10764015365562</v>
+        <v>15.4097576417308</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7972597693001825</v>
+        <v>0.5106125488735803</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1517261825718705</v>
+        <v>-0.2289029807228925</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6790</v>
+        <v>6625</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>122.1190003559968</v>
+        <v>237.9542029357949</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>38.05</v>
+        <v>77</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.22944887494322</v>
+        <v>50.15690950772957</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.32640091879365</v>
+        <v>10.03662350012338</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.037586572216821</v>
+        <v>0.8474926211414581</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0563574521660849</v>
+        <v>0.06807974606334589</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6504</v>
+        <v>6757</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>114.9978729070872</v>
+        <v>233.7473577959741</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>37.85</v>
+        <v>55.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.59281436138902</v>
+        <v>44.02417929581536</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.11253101704855</v>
+        <v>7.837136322467738</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.062031496763574</v>
+        <v>1.247799484921084</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0819252409539189</v>
+        <v>0.033782793704897</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6838</v>
+        <v>6835</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>98.30895552553424</v>
+        <v>232.6713416645746</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>23.2</v>
+        <v>31.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.83055699010896</v>
+        <v>46.50835623791816</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.31109486438781</v>
+        <v>18.10764011538595</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8980834186566619</v>
+        <v>0.7972597693001825</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0567686169859612</v>
+        <v>0.1517261825814085</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6754</v>
+        <v>6570</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>92.59363839205643</v>
+        <v>231.3860964970726</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>41.8</v>
+        <v>51.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.89406996508243</v>
+        <v>41.76763353698689</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.48617970673438</v>
+        <v>13.11805404178261</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9745354840591548</v>
+        <v>0.633802202302688</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,62 +6294,963 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.066625455489744</v>
+        <v>-0.5384795745615585</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
+        <v>6546</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>正基</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>218.7434976496474</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>52.88236989375744</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>18.06068705048132</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.6276581417216501</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.4254912189491022</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6592</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>和潤企業</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>215.6799505614673</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>45.89200527279498</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>11.32339210233487</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1.42796065595693</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.0644372956530137</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6720</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>久昌</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>210.1874719835189</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>43.39354730435592</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>26.21492101012895</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.929394978777252</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>-0.149747440881707</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>欣普羅</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>205.463684471994</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>50.40058033267854</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>21.42041206701624</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.285201701298458</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.2901450151605744</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6550</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>北極星藥業-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>196.8224937055401</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>47.256877009071</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>28.05998069989893</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.8042719887368431</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.1225559272054018</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6776</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>171.2101962687045</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>43.00466960646463</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>15.70895638231258</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.3638652344808326</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0299615602255606</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6641</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>基士德-KY</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>165.2938462010435</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>43.79507780811872</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>8.805237687434296</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6633244662710593</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0104962762871173</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6667</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>信紘科</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>164.6092193858476</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>41.2073809375667</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>29.6634944511685</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.7623102678039883</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.8422647863196691</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>6725</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>矽科宏晟</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>162.9480484125874</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>39.01009972197818</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>30.24332614770899</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.585394433467616</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>2.172077716486065</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>6799</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>來頡</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>151.0337240580648</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>44.90322747381586</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>15.55438173008736</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.6289056521666977</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>0.2579152567941127</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>泰福-KY</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>147.8752817203152</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>40.62668117748802</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>11.96892761854684</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.423218635419374</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.0104760226878446</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>145.9864144070126</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>39.04079943809308</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>8.64849029622107</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>1.447967948046507</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.1412595636217252</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6684</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>安格</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>133.3683247401822</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>46.15560368970116</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>11.72733102486306</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.8523813156250838</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.1377780762125111</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6790</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>永豐實</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>122.1190003559968</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>43.22944886062307</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>13.32640091879365</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1.037586572216821</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0563574521851612</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>南六</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>114.9978729070872</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>48.59281439842147</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>16.11253109930331</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.062031496763574</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.08192524104931111</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>98.30895552553424</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>47.83055652938694</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>11.31109497445349</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.8980834186566619</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>0.0567686170241158</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6754</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>匯僑設計</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>92.59363839205672</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>44.8940699518784</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>13.48618008011975</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.9745354840591548</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0666254553752688</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6823</v>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>濾能</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>88.41192889419995</v>
-      </c>
-      <c r="E111" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>88.41192889419737</v>
+      </c>
+      <c r="E128" s="2" t="n">
         <v>61.6</v>
       </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>41.62467790726652</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>17.72258441619948</v>
-      </c>
-      <c r="J111" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>41.62467792062706</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>17.72258445609132</v>
+      </c>
+      <c r="J128" s="2" t="n">
         <v>3.203028548743016</v>
       </c>
-      <c r="K111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>0.0455699270230985</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0455699269277023</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
